--- a/nr-update-patient-name/ig/CodeSystem-fr-core-cs-v2-3307.xlsx
+++ b/nr-update-patient-name/ig/CodeSystem-fr-core-cs-v2-3307.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T13:41:02+00:00</t>
+    <t>2025-02-17T10:02:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
